--- a/branches/migration/2026.0.0-template-v0.13.2/StructureDefinition-f675b1e8-9f3f-44e8-bb59-9681f78eb464.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.2/StructureDefinition-f675b1e8-9f3f-44e8-bb59-9681f78eb464.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.0.0</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
